--- a/data/tags/סינגלים חדשים/global/2026-03-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-03-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L12"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>נטע ברזילי – גם זה יגיע</v>
+        <v>שרית חדד - Mamma Mia</v>
       </c>
       <c r="B2" t="str">
         <v>2026-03-15</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a0%d7%98%d7%a2-%d7%91%d7%a8%d7%96%d7%99%d7%9c%d7%99-%d7%92%d7%9d-%d7%96%d7%94-%d7%99%d7%92%d7%99%d7%a2/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410015&amp;sid=64ffd39bf093175dd74966d37c559395</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-15</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>את נטע ברזילי מעולם לא שמענו כל כך נרגשת וכאובה. “גם זה יגיע” הוא שיר החמצה שנשען על פרדוקס כואב מאוד: יש רצון לאהוב, יש אפילו הבטחה לאהוב, אבל אין יכולת ממשית לממש את האהבה בהווה. זה מה שהופך אותו</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,392 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>נטע ברזילי – גם זה יגיע</v>
+        <v>שרית חדד - Mamma Mia</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>שראל סופר - מדויק ולא בערך</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-03-15</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410014&amp;sid=64ffd39bf093175dd74966d37c559395</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-03-15</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>שראל סופר - מדויק ולא בערך</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>שמוליק סוכות - אבא טוב</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-03-15</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410013&amp;sid=64ffd39bf093175dd74966d37c559395</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-03-15</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>שמוליק סוכות - אבא טוב</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>שירה ואן ופרן - ייפול עליי</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-03-15</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410012&amp;sid=64ffd39bf093175dd74966d37c559395</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-03-15</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>שירה ואן ופרן - ייפול עליי</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>רון דבני - מה אני אגיד לך</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-03-15</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410011&amp;sid=64ffd39bf093175dd74966d37c559395</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-03-15</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>רון דבני - מה אני אגיד לך</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>נטע ברזילי - גם זה יגיע</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-03-15</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410010&amp;sid=64ffd39bf093175dd74966d37c559395</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-03-15</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>נטע ברזילי - גם זה יגיע</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>מאי כהן - אנשים</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-03-15</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410009&amp;sid=64ffd39bf093175dd74966d37c559395</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-03-15</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>מאי כהן - אנשים</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>איציק סנדרוי - תנו לי אוויר</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-03-15</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410008&amp;sid=64ffd39bf093175dd74966d37c559395</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-03-15</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>איציק סנדרוי - תנו לי אוויר</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>אהרון סיטבון - ניגון יהודי</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-03-15</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410007&amp;sid=64ffd39bf093175dd74966d37c559395</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-03-15</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>אהרון סיטבון - ניגון יהודי</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>אבישי אזיקרי - לימונדה</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-03-15</v>
+      </c>
+      <c r="C11" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410006&amp;sid=64ffd39bf093175dd74966d37c559395</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-03-15</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>אבישי אזיקרי - לימונדה</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>אבי אילסון - בזכותם</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-03-15</v>
+      </c>
+      <c r="C12" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410005&amp;sid=64ffd39bf093175dd74966d37c559395</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-03-15</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>אבי אילסון - בזכותם</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L12"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-03-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-03-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שרית חדד - Mamma Mia</v>
+        <v>רון דבני – מה אני אגיד לך</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410015&amp;sid=64ffd39bf093175dd74966d37c559395</v>
+        <v>https://yosmusic.com/%d7%a8%d7%95%d7%9f-%d7%93%d7%91%d7%a0%d7%99-%d7%9e%d7%94-%d7%90%d7%a0%d7%99-%d7%90%d7%92%d7%99%d7%93-%d7%9c%d7%9a/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>רון דבני שר שיר מחאה חד, חכם ומטריד, שפועל במסווה של שיר קצבי כמעט קליל, אבל בתוכו יושב טקסט אפל מאוד על כוח, הדחקה, חרדה מחשיפה, והתפוררות של מנגנוני הגנה גבריים. זה בדיוק אחד הכוחות שלו: המוזיקה עולה על “נתיב</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,392 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שרית חדד - Mamma Mia</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>שראל סופר - מדויק ולא בערך</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-03-15</v>
-      </c>
-      <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410014&amp;sid=64ffd39bf093175dd74966d37c559395</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-03-15</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>שראל סופר - מדויק ולא בערך</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>שמוליק סוכות - אבא טוב</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-03-15</v>
-      </c>
-      <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410013&amp;sid=64ffd39bf093175dd74966d37c559395</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-03-15</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>שמוליק סוכות - אבא טוב</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>שירה ואן ופרן - ייפול עליי</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-03-15</v>
-      </c>
-      <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410012&amp;sid=64ffd39bf093175dd74966d37c559395</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-03-15</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>שירה ואן ופרן - ייפול עליי</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>רון דבני - מה אני אגיד לך</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-03-15</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410011&amp;sid=64ffd39bf093175dd74966d37c559395</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-03-15</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>רון דבני - מה אני אגיד לך</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>נטע ברזילי - גם זה יגיע</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-03-15</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410010&amp;sid=64ffd39bf093175dd74966d37c559395</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-03-15</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>נטע ברזילי - גם זה יגיע</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>מאי כהן - אנשים</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-03-15</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410009&amp;sid=64ffd39bf093175dd74966d37c559395</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-03-15</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>מאי כהן - אנשים</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>איציק סנדרוי - תנו לי אוויר</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-03-15</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410008&amp;sid=64ffd39bf093175dd74966d37c559395</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-03-15</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>איציק סנדרוי - תנו לי אוויר</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>אהרון סיטבון - ניגון יהודי</v>
-      </c>
-      <c r="B10" t="str">
-        <v>2026-03-15</v>
-      </c>
-      <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410007&amp;sid=64ffd39bf093175dd74966d37c559395</v>
-      </c>
-      <c r="D10" t="str">
-        <v>2026-03-15</v>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-      <c r="H10" t="str">
-        <v/>
-      </c>
-      <c r="I10" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J10" t="str">
-        <v/>
-      </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
-      <c r="L10" t="str">
-        <v>אהרון סיטבון - ניגון יהודי</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>אבישי אזיקרי - לימונדה</v>
-      </c>
-      <c r="B11" t="str">
-        <v>2026-03-15</v>
-      </c>
-      <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410006&amp;sid=64ffd39bf093175dd74966d37c559395</v>
-      </c>
-      <c r="D11" t="str">
-        <v>2026-03-15</v>
-      </c>
-      <c r="E11" t="str">
-        <v/>
-      </c>
-      <c r="F11" t="str">
-        <v/>
-      </c>
-      <c r="G11" t="str">
-        <v/>
-      </c>
-      <c r="H11" t="str">
-        <v/>
-      </c>
-      <c r="I11" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J11" t="str">
-        <v/>
-      </c>
-      <c r="K11" t="str">
-        <v/>
-      </c>
-      <c r="L11" t="str">
-        <v>אבישי אזיקרי - לימונדה</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>אבי אילסון - בזכותם</v>
-      </c>
-      <c r="B12" t="str">
-        <v>2026-03-15</v>
-      </c>
-      <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410005&amp;sid=64ffd39bf093175dd74966d37c559395</v>
-      </c>
-      <c r="D12" t="str">
-        <v>2026-03-15</v>
-      </c>
-      <c r="E12" t="str">
-        <v/>
-      </c>
-      <c r="F12" t="str">
-        <v/>
-      </c>
-      <c r="G12" t="str">
-        <v/>
-      </c>
-      <c r="H12" t="str">
-        <v/>
-      </c>
-      <c r="I12" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J12" t="str">
-        <v/>
-      </c>
-      <c r="K12" t="str">
-        <v/>
-      </c>
-      <c r="L12" t="str">
-        <v>אבי אילסון - בזכותם</v>
+        <v>רון דבני – מה אני אגיד לך</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-03-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-03-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L16"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>רון דבני – מה אני אגיד לך</v>
+        <v>שלום ממן - יא רייח</v>
       </c>
       <c r="B2" t="str">
         <v>2026-03-16</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a8%d7%95%d7%9f-%d7%93%d7%91%d7%a0%d7%99-%d7%9e%d7%94-%d7%90%d7%a0%d7%99-%d7%90%d7%92%d7%99%d7%93-%d7%9c%d7%9a/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410031&amp;sid=ffdf5a86de96ff39379f883bfca9bcca</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-16</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>רון דבני שר שיר מחאה חד, חכם ומטריד, שפועל במסווה של שיר קצבי כמעט קליל, אבל בתוכו יושב טקסט אפל מאוד על כוח, הדחקה, חרדה מחשיפה, והתפוררות של מנגנוני הגנה גבריים. זה בדיוק אחד הכוחות שלו: המוזיקה עולה על “נתיב</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,544 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>רון דבני – מה אני אגיד לך</v>
+        <v>שלום ממן - יא רייח</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>שלו משען - אגם של טעויות</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-03-16</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410030&amp;sid=ffdf5a86de96ff39379f883bfca9bcca</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-03-16</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>שלו משען - אגם של טעויות</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>שיר מזרחי &amp; משה זאודה - יש לנו כאב</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-03-16</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410029&amp;sid=ffdf5a86de96ff39379f883bfca9bcca</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-03-16</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>שיר מזרחי &amp; משה זאודה - יש לנו כאב</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>קיליאן ג'אמי - צלקת</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-03-16</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410028&amp;sid=ffdf5a86de96ff39379f883bfca9bcca</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-03-16</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>קיליאן ג'אמי - צלקת</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>צחי אלוש - טיקי טקה</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-03-16</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410027&amp;sid=ffdf5a86de96ff39379f883bfca9bcca</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-03-16</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>צחי אלוש - טיקי טקה</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>עידן משה - ריגוש וכאב</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-03-16</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410026&amp;sid=ffdf5a86de96ff39379f883bfca9bcca</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-03-16</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>עידן משה - ריגוש וכאב</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>עידו כנפי - פרפרים בבטן</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-03-16</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410025&amp;sid=ffdf5a86de96ff39379f883bfca9bcca</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-03-16</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>עידו כנפי - פרפרים בבטן</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>סגיב כהן - חסד יסובבנו</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-03-16</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410024&amp;sid=ffdf5a86de96ff39379f883bfca9bcca</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-03-16</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>סגיב כהן - חסד יסובבנו</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>נתנאל מלכה - בלעדייך</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-03-16</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410023&amp;sid=ffdf5a86de96ff39379f883bfca9bcca</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-03-16</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>נתנאל מלכה - בלעדייך</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>מיכה ינון - מחרוזת חזון אחרית הימים 2026</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-03-16</v>
+      </c>
+      <c r="C11" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410022&amp;sid=ffdf5a86de96ff39379f883bfca9bcca</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-03-16</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>מיכה ינון - מחרוזת חזון אחרית הימים 2026</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>יהורם גאון - עד עולם</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-03-16</v>
+      </c>
+      <c r="C12" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410021&amp;sid=ffdf5a86de96ff39379f883bfca9bcca</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-03-16</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>יהורם גאון - עד עולם</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>דיויד טויב &amp; רפאל מדמון - עושה השלום</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2026-03-16</v>
+      </c>
+      <c r="C13" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410020&amp;sid=ffdf5a86de96ff39379f883bfca9bcca</v>
+      </c>
+      <c r="D13" t="str">
+        <v>2026-03-16</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v>דיויד טויב &amp; רפאל מדמון - עושה השלום</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>גבריאל שרם - שוברת גלים</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2026-03-16</v>
+      </c>
+      <c r="C14" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410019&amp;sid=ffdf5a86de96ff39379f883bfca9bcca</v>
+      </c>
+      <c r="D14" t="str">
+        <v>2026-03-16</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <v>גבריאל שרם - שוברת גלים</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>אורי ספז - תפילה שלך</v>
+      </c>
+      <c r="B15" t="str">
+        <v>2026-03-16</v>
+      </c>
+      <c r="C15" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410018&amp;sid=ffdf5a86de96ff39379f883bfca9bcca</v>
+      </c>
+      <c r="D15" t="str">
+        <v>2026-03-16</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <v/>
+      </c>
+      <c r="L15" t="str">
+        <v>אורי ספז - תפילה שלך</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>אבי שפרונג - הבית שלי</v>
+      </c>
+      <c r="B16" t="str">
+        <v>2026-03-16</v>
+      </c>
+      <c r="C16" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410017&amp;sid=ffdf5a86de96ff39379f883bfca9bcca</v>
+      </c>
+      <c r="D16" t="str">
+        <v>2026-03-16</v>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
+      <c r="K16" t="str">
+        <v/>
+      </c>
+      <c r="L16" t="str">
+        <v>אבי שפרונג - הבית שלי</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L16"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-03-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-03-week03/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>יהורם גאון – עד עולם</v>
+        <v>מכלוף – תשמור עליי</v>
       </c>
       <c r="B2" t="str">
         <v>2026-03-17</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%99%d7%94%d7%95%d7%a8%d7%9d-%d7%92%d7%90%d7%95%d7%9f-%d7%a2%d7%93-%d7%a2%d7%95%d7%9c%d7%9d/</v>
+        <v>https://yosmusic.com/%d7%9e%d7%9b%d7%9c%d7%95%d7%a3-%d7%aa%d7%a9%d7%9e%d7%95%d7%a8-%d7%a2%d7%9c%d7%99%d7%99/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-17</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר ששר יהורם גאון יושב על התפר שבין נוסטלגיה ישראלית קלאסית לבין עדכון עכשווי – וזה מורגש גם ברמת המילים וגם ברמת ההקשר. על פניו זה שיר אהבה בין גבר לאישה – “שלך הנני”, “את לעד תהיי לי”. אבל יש</v>
+        <v>הקאבר של “תשמור עליי” של מכלוף לשיר “תשמור על העולם ילד” של דוד ד'אור הוא לא רק ביצוע מחדש – אלא פרשנות רגשית ועדכנית שמזיזה את מרכז הכובד של השיר. הגרסה החדשה היא פחות תמימה, יותר חשופה, ופונה פנימה במקום</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>יהורם גאון – עד עולם</v>
+        <v>מכלוף – תשמור עליי</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/global/2026-03-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-03-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L10"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>מכלוף – תשמור עליי</v>
+        <v>שרון זריהן - רק תזכרי</v>
       </c>
       <c r="B2" t="str">
         <v>2026-03-17</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%9e%d7%9b%d7%9c%d7%95%d7%a3-%d7%aa%d7%a9%d7%9e%d7%95%d7%a8-%d7%a2%d7%9c%d7%99%d7%99/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410040&amp;sid=1318ce939be672e5827fe3d26c7987b5</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-17</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>הקאבר של “תשמור עליי” של מכלוף לשיר “תשמור על העולם ילד” של דוד ד'אור הוא לא רק ביצוע מחדש – אלא פרשנות רגשית ועדכנית שמזיזה את מרכז הכובד של השיר. הגרסה החדשה היא פחות תמימה, יותר חשופה, ופונה פנימה במקום</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,316 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>מכלוף – תשמור עליי</v>
+        <v>שרון זריהן - רק תזכרי</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>עילי בוטנר והילדים החדשים - בוא לאור</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-03-17</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410039&amp;sid=1318ce939be672e5827fe3d26c7987b5</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-03-17</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>עילי בוטנר והילדים החדשים - בוא לאור</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>נופר נחמני - משמעות</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-03-17</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410038&amp;sid=1318ce939be672e5827fe3d26c7987b5</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-03-17</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>נופר נחמני - משמעות</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>נהוראי זנטי - מי מספר לך</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-03-17</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410037&amp;sid=1318ce939be672e5827fe3d26c7987b5</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-03-17</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>נהוראי זנטי - מי מספר לך</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>מור נדין - נזכרת בעבר</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-03-17</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410036&amp;sid=1318ce939be672e5827fe3d26c7987b5</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-03-17</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>מור נדין - נזכרת בעבר</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>לינוי כהן - עד הסוף</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-03-17</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410035&amp;sid=1318ce939be672e5827fe3d26c7987b5</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-03-17</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>לינוי כהן - עד הסוף</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>גל ג'ומה - קוקוריקו</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-03-17</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410034&amp;sid=1318ce939be672e5827fe3d26c7987b5</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-03-17</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>גל ג'ומה - קוקוריקו</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>ג'ולייטה - אמא שלי</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-03-17</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410033&amp;sid=1318ce939be672e5827fe3d26c7987b5</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-03-17</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>ג'ולייטה - אמא שלי</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>אופק כהן - ברגעים שהתפרקתי</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-03-17</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410032&amp;sid=1318ce939be672e5827fe3d26c7987b5</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-03-17</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>אופק כהן - ברגעים שהתפרקתי</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L10"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-03-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-03-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שרון זריהן - רק תזכרי</v>
+        <v>תמר כהנא - לנצנץ</v>
       </c>
       <c r="B2" t="str">
         <v>2026-03-17</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410040&amp;sid=1318ce939be672e5827fe3d26c7987b5</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410041&amp;sid=abad36e6439a3c11a22b9564f2a3015c</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,316 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שרון זריהן - רק תזכרי</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>עילי בוטנר והילדים החדשים - בוא לאור</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-03-17</v>
-      </c>
-      <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410039&amp;sid=1318ce939be672e5827fe3d26c7987b5</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-03-17</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>עילי בוטנר והילדים החדשים - בוא לאור</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>נופר נחמני - משמעות</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-03-17</v>
-      </c>
-      <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410038&amp;sid=1318ce939be672e5827fe3d26c7987b5</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-03-17</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>נופר נחמני - משמעות</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>נהוראי זנטי - מי מספר לך</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-03-17</v>
-      </c>
-      <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410037&amp;sid=1318ce939be672e5827fe3d26c7987b5</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-03-17</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>נהוראי זנטי - מי מספר לך</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>מור נדין - נזכרת בעבר</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-03-17</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410036&amp;sid=1318ce939be672e5827fe3d26c7987b5</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-03-17</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>מור נדין - נזכרת בעבר</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>לינוי כהן - עד הסוף</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-03-17</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410035&amp;sid=1318ce939be672e5827fe3d26c7987b5</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-03-17</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>לינוי כהן - עד הסוף</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>גל ג'ומה - קוקוריקו</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-03-17</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410034&amp;sid=1318ce939be672e5827fe3d26c7987b5</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-03-17</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>גל ג'ומה - קוקוריקו</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>ג'ולייטה - אמא שלי</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-03-17</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410033&amp;sid=1318ce939be672e5827fe3d26c7987b5</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-03-17</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>ג'ולייטה - אמא שלי</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>אופק כהן - ברגעים שהתפרקתי</v>
-      </c>
-      <c r="B10" t="str">
-        <v>2026-03-17</v>
-      </c>
-      <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410032&amp;sid=1318ce939be672e5827fe3d26c7987b5</v>
-      </c>
-      <c r="D10" t="str">
-        <v>2026-03-17</v>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-      <c r="H10" t="str">
-        <v/>
-      </c>
-      <c r="I10" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J10" t="str">
-        <v/>
-      </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
-      <c r="L10" t="str">
-        <v>אופק כהן - ברגעים שהתפרקתי</v>
+        <v>תמר כהנא - לנצנץ</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-03-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-03-week03/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>תמר כהנא - לנצנץ</v>
+        <v>עילי בוטנר והילדים החדשים – בוא לאור</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410041&amp;sid=abad36e6439a3c11a22b9564f2a3015c</v>
+        <v>https://yosmusic.com/%d7%a2%d7%99%d7%9c%d7%99-%d7%91%d7%95%d7%98%d7%a0%d7%a8-%d7%95%d7%94%d7%99%d7%9c%d7%93%d7%99%d7%9d-%d7%94%d7%97%d7%93%d7%a9%d7%99%d7%9d-%d7%91%d7%95%d7%90-%d7%9c%d7%90%d7%95%d7%a8/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-18</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>השיר הוא דוגמה מדויקת למה שעילי בוטנר עושה כבר שנים – אבל כאן, בתוך תקופה טעונה וקשה, הןא מקבל משמעות אחרת: פחות “שיר נעים”, יותר שיר הישרדות רגשי. זה שיר שמכוון להיות פשוט – אבל מתחת לפשטות יש כמיהה עמוקה</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>תמר כהנא - לנצנץ</v>
+        <v>עילי בוטנר והילדים החדשים – בוא לאור</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/global/2026-03-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-03-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>עילי בוטנר והילדים החדשים – בוא לאור</v>
+        <v>מוישי פרסברגר - מחרוזת דיבורים של אמונה 2026</v>
       </c>
       <c r="B2" t="str">
         <v>2026-03-18</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a2%d7%99%d7%9c%d7%99-%d7%91%d7%95%d7%98%d7%a0%d7%a8-%d7%95%d7%94%d7%99%d7%9c%d7%93%d7%99%d7%9d-%d7%94%d7%97%d7%93%d7%a9%d7%99%d7%9d-%d7%91%d7%95%d7%90-%d7%9c%d7%90%d7%95%d7%a8/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410047&amp;sid=280407f62833e0c339548612e2fd2cd7</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-18</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר הוא דוגמה מדויקת למה שעילי בוטנר עושה כבר שנים – אבל כאן, בתוך תקופה טעונה וקשה, הןא מקבל משמעות אחרת: פחות “שיר נעים”, יותר שיר הישרדות רגשי. זה שיר שמכוון להיות פשוט – אבל מתחת לפשטות יש כמיהה עמוקה</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,202 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>עילי בוטנר והילדים החדשים – בוא לאור</v>
+        <v>מוישי פרסברגר - מחרוזת דיבורים של אמונה 2026</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>ליאם דיין - שקט בלב</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-03-18</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410046&amp;sid=280407f62833e0c339548612e2fd2cd7</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-03-18</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>ליאם דיין - שקט בלב</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>יוסי פריד - איך קען</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-03-18</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410045&amp;sid=280407f62833e0c339548612e2fd2cd7</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-03-18</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>יוסי פריד - איך קען</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>יובל מזרחי - דואט</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-03-18</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410044&amp;sid=280407f62833e0c339548612e2fd2cd7</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-03-18</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>יובל מזרחי - דואט</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>דניאל נורני - גלגולים</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-03-18</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410043&amp;sid=280407f62833e0c339548612e2fd2cd7</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-03-18</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>דניאל נורני - גלגולים</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>אמיר אליהו - מחרוזת הלל 2026</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-03-18</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410042&amp;sid=280407f62833e0c339548612e2fd2cd7</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-03-18</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>אמיר אליהו - מחרוזת הלל 2026</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L7"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-03-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-03-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>מוישי פרסברגר - מחרוזת דיבורים של אמונה 2026</v>
+        <v>פינחס מלך - אוֹר הָאַהֲבָה הָאֱלֹהִית</v>
       </c>
       <c r="B2" t="str">
         <v>2026-03-18</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410047&amp;sid=280407f62833e0c339548612e2fd2cd7</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410050&amp;sid=0f9be58e618ad79684191ea4a57e6593</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>מוישי פרסברגר - מחרוזת דיבורים של אמונה 2026</v>
+        <v>פינחס מלך - אוֹר הָאַהֲבָה הָאֱלֹהִית</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>ליאם דיין - שקט בלב</v>
+        <v>עלי הרטום - צוק</v>
       </c>
       <c r="B3" t="str">
         <v>2026-03-18</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410046&amp;sid=280407f62833e0c339548612e2fd2cd7</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410049&amp;sid=0f9be58e618ad79684191ea4a57e6593</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>ליאם דיין - שקט בלב</v>
+        <v>עלי הרטום - צוק</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>יוסי פריד - איך קען</v>
+        <v>עידן דוכן - מסע רגשי</v>
       </c>
       <c r="B4" t="str">
         <v>2026-03-18</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410045&amp;sid=280407f62833e0c339548612e2fd2cd7</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410048&amp;sid=0f9be58e618ad79684191ea4a57e6593</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,126 +545,12 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>יוסי פריד - איך קען</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>יובל מזרחי - דואט</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-03-18</v>
-      </c>
-      <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410044&amp;sid=280407f62833e0c339548612e2fd2cd7</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-03-18</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>יובל מזרחי - דואט</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>דניאל נורני - גלגולים</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-03-18</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410043&amp;sid=280407f62833e0c339548612e2fd2cd7</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-03-18</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>דניאל נורני - גלגולים</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>אמיר אליהו - מחרוזת הלל 2026</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-03-18</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410042&amp;sid=280407f62833e0c339548612e2fd2cd7</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-03-18</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>אמיר אליהו - מחרוזת הלל 2026</v>
+        <v>עידן דוכן - מסע רגשי</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-03-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-03-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>פינחס מלך - אוֹר הָאַהֲבָה הָאֱלֹהִית</v>
+        <v>תמר כהנא – לנצנץ</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410050&amp;sid=0f9be58e618ad79684191ea4a57e6593</v>
+        <v>https://yosmusic.com/%d7%aa%d7%9e%d7%a8-%d7%9b%d7%94%d7%a0%d7%90-%d7%9c%d7%a0%d7%a6%d7%a0%d7%a5/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-19</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>השיר “לנצנץ” של תמר כהנא מתבססת פחות על “מבנה פופ” ויותר על תודעה מתפרקת בזמן אמת. זה לא שיר שמנסה להיות יפה – אלא כזה שחותר להיות אמיתי, חשוף מאוד –  גם אם זה לא נוח. זה שיר על קשר</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,88 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>פינחס מלך - אוֹר הָאַהֲבָה הָאֱלֹהִית</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>עלי הרטום - צוק</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-03-18</v>
-      </c>
-      <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410049&amp;sid=0f9be58e618ad79684191ea4a57e6593</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-03-19</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>עלי הרטום - צוק</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>עידן דוכן - מסע רגשי</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-03-18</v>
-      </c>
-      <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410048&amp;sid=0f9be58e618ad79684191ea4a57e6593</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-03-19</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>עידן דוכן - מסע רגשי</v>
+        <v>תמר כהנא – לנצנץ</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-03-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-03-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>תמר כהנא – לנצנץ</v>
+        <v>אשר גבאי - שירת המונים - אחת שאלתי</v>
       </c>
       <c r="B2" t="str">
         <v>2026-03-19</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%aa%d7%9e%d7%a8-%d7%9b%d7%94%d7%a0%d7%90-%d7%9c%d7%a0%d7%a6%d7%a0%d7%a5/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410056&amp;sid=746bcaca46b314a4372c05f7bdb94eaa</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-19</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר “לנצנץ” של תמר כהנא מתבססת פחות על “מבנה פופ” ויותר על תודעה מתפרקת בזמן אמת. זה לא שיר שמנסה להיות יפה – אלא כזה שחותר להיות אמיתי, חשוף מאוד –  גם אם זה לא נוח. זה שיר על קשר</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,50 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>תמר כהנא – לנצנץ</v>
+        <v>אשר גבאי - שירת המונים - אחת שאלתי</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>אדווה עומר - רק אלייך</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-03-19</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410055&amp;sid=746bcaca46b314a4372c05f7bdb94eaa</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-03-19</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>אדווה עומר - רק אלייך</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-03-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-03-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אשר גבאי - שירת המונים - אחת שאלתי</v>
+        <v>מכלוף - תשמור עליי</v>
       </c>
       <c r="B2" t="str">
         <v>2026-03-19</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410056&amp;sid=746bcaca46b314a4372c05f7bdb94eaa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410064&amp;sid=811de4f9ec95ebc290c8d82901e5655f</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-19</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אשר גבאי - שירת המונים - אחת שאלתי</v>
+        <v>מכלוף - תשמור עליי</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>אדווה עומר - רק אלייך</v>
+        <v>מיקי בן עטר - מחרוזת מזמורי שבת 2026</v>
       </c>
       <c r="B3" t="str">
         <v>2026-03-19</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410055&amp;sid=746bcaca46b314a4372c05f7bdb94eaa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410063&amp;sid=811de4f9ec95ebc290c8d82901e5655f</v>
       </c>
       <c r="D3" t="str">
         <v>2026-03-19</v>
@@ -507,12 +507,240 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>אדווה עומר - רק אלייך</v>
+        <v>מיקי בן עטר - מחרוזת מזמורי שבת 2026</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>ליאן ניגרין - נפש תאומה קאבר</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-03-19</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410062&amp;sid=811de4f9ec95ebc290c8d82901e5655f</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-03-19</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>ליאן ניגרין - נפש תאומה קאבר</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>יגאל עדי - מחרוזת עגילי זהב 2026</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-03-19</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410061&amp;sid=811de4f9ec95ebc290c8d82901e5655f</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-03-19</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>יגאל עדי - מחרוזת עגילי זהב 2026</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>טל לוי - אופוריה משקרת</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-03-19</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410060&amp;sid=811de4f9ec95ebc290c8d82901e5655f</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-03-19</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>טל לוי - אופוריה משקרת</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>דורון רוקח - מחרוזת נעורים 2026</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-03-19</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410059&amp;sid=811de4f9ec95ebc290c8d82901e5655f</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-03-19</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>דורון רוקח - מחרוזת נעורים 2026</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>דולב שמחי - לילה מאוחר</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-03-19</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410058&amp;sid=811de4f9ec95ebc290c8d82901e5655f</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-03-19</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>דולב שמחי - לילה מאוחר</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>גלית סדן &amp; שר-אל - אם את רווקה 2026</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-03-19</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410057&amp;sid=811de4f9ec95ebc290c8d82901e5655f</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-03-19</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>גלית סדן &amp; שר-אל - אם את רווקה 2026</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-03-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-03-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>מכלוף - תשמור עליי</v>
+        <v>תמר ריילי &amp; לירן דנינו - בת של מלך</v>
       </c>
       <c r="B2" t="str">
         <v>2026-03-19</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410064&amp;sid=811de4f9ec95ebc290c8d82901e5655f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410070&amp;sid=d1f963fe2cdb04d44984e4c96de62fe7</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-19</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>מכלוף - תשמור עליי</v>
+        <v>תמר ריילי &amp; לירן דנינו - בת של מלך</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>מיקי בן עטר - מחרוזת מזמורי שבת 2026</v>
+        <v>שר-אל - זמן</v>
       </c>
       <c r="B3" t="str">
         <v>2026-03-19</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410063&amp;sid=811de4f9ec95ebc290c8d82901e5655f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410069&amp;sid=d1f963fe2cdb04d44984e4c96de62fe7</v>
       </c>
       <c r="D3" t="str">
         <v>2026-03-19</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>מיקי בן עטר - מחרוזת מזמורי שבת 2026</v>
+        <v>שר-אל - זמן</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ליאן ניגרין - נפש תאומה קאבר</v>
+        <v>שמואל - אני מבורך</v>
       </c>
       <c r="B4" t="str">
         <v>2026-03-19</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410062&amp;sid=811de4f9ec95ebc290c8d82901e5655f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410068&amp;sid=d1f963fe2cdb04d44984e4c96de62fe7</v>
       </c>
       <c r="D4" t="str">
         <v>2026-03-19</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>ליאן ניגרין - נפש תאומה קאבר</v>
+        <v>שמואל - אני מבורך</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>יגאל עדי - מחרוזת עגילי זהב 2026</v>
+        <v>שיר לוי - אהבתי באמת</v>
       </c>
       <c r="B5" t="str">
         <v>2026-03-19</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410061&amp;sid=811de4f9ec95ebc290c8d82901e5655f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410067&amp;sid=d1f963fe2cdb04d44984e4c96de62fe7</v>
       </c>
       <c r="D5" t="str">
         <v>2026-03-19</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>יגאל עדי - מחרוזת עגילי זהב 2026</v>
+        <v>שיר לוי - אהבתי באמת</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>טל לוי - אופוריה משקרת</v>
+        <v>רני רחמים - נושאות עיניי תפילה</v>
       </c>
       <c r="B6" t="str">
         <v>2026-03-19</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410060&amp;sid=811de4f9ec95ebc290c8d82901e5655f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410066&amp;sid=d1f963fe2cdb04d44984e4c96de62fe7</v>
       </c>
       <c r="D6" t="str">
         <v>2026-03-19</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>טל לוי - אופוריה משקרת</v>
+        <v>רני רחמים - נושאות עיניי תפילה</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>דורון רוקח - מחרוזת נעורים 2026</v>
+        <v>רג'ה &amp; נתי אפ אמ - מסובב הסיבות</v>
       </c>
       <c r="B7" t="str">
         <v>2026-03-19</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410059&amp;sid=811de4f9ec95ebc290c8d82901e5655f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410065&amp;sid=d1f963fe2cdb04d44984e4c96de62fe7</v>
       </c>
       <c r="D7" t="str">
         <v>2026-03-19</v>
@@ -659,88 +659,12 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>דורון רוקח - מחרוזת נעורים 2026</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>דולב שמחי - לילה מאוחר</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-03-19</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410058&amp;sid=811de4f9ec95ebc290c8d82901e5655f</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-03-19</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>דולב שמחי - לילה מאוחר</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>גלית סדן &amp; שר-אל - אם את רווקה 2026</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-03-19</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410057&amp;sid=811de4f9ec95ebc290c8d82901e5655f</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-03-19</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>גלית סדן &amp; שר-אל - אם את רווקה 2026</v>
+        <v>רג'ה &amp; נתי אפ אמ - מסובב הסיבות</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L7"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-03-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-03-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L17"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>תמר ריילי &amp; לירן דנינו - בת של מלך</v>
+        <v>רועי שמואלי - נרקומן של רגשות</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410070&amp;sid=d1f963fe2cdb04d44984e4c96de62fe7</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410087&amp;sid=05206eacbe62b6bb574609b11b437bc0</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>תמר ריילי &amp; לירן דנינו - בת של מלך</v>
+        <v>רועי שמואלי - נרקומן של רגשות</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>שר-אל - זמן</v>
+        <v>רומי רון - עד שאשוב</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410069&amp;sid=d1f963fe2cdb04d44984e4c96de62fe7</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410086&amp;sid=05206eacbe62b6bb574609b11b437bc0</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>שר-אל - זמן</v>
+        <v>רומי רון - עד שאשוב</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>שמואל - אני מבורך</v>
+        <v>רוחמה רז - אל האור</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410068&amp;sid=d1f963fe2cdb04d44984e4c96de62fe7</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410085&amp;sid=05206eacbe62b6bb574609b11b437bc0</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>שמואל - אני מבורך</v>
+        <v>רוחמה רז - אל האור</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>שיר לוי - אהבתי באמת</v>
+        <v>נחמן סבג מארח את פייגה סבג - מחרוזת ממשיך את החיים 2026</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410067&amp;sid=d1f963fe2cdb04d44984e4c96de62fe7</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410084&amp;sid=05206eacbe62b6bb574609b11b437bc0</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,21 +583,21 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>שיר לוי - אהבתי באמת</v>
+        <v>נחמן סבג מארח את פייגה סבג - מחרוזת ממשיך את החיים 2026</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>רני רחמים - נושאות עיניי תפילה</v>
+        <v>משה זרצקי - האמונה נותנת כח</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410066&amp;sid=d1f963fe2cdb04d44984e4c96de62fe7</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410083&amp;sid=05206eacbe62b6bb574609b11b437bc0</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -621,21 +621,21 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>רני רחמים - נושאות עיניי תפילה</v>
+        <v>משה זרצקי - האמונה נותנת כח</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>רג'ה &amp; נתי אפ אמ - מסובב הסיבות</v>
+        <v>מייק מנג'ו - מחרוזת מלכת המועדון 2026</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410065&amp;sid=d1f963fe2cdb04d44984e4c96de62fe7</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410082&amp;sid=05206eacbe62b6bb574609b11b437bc0</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -659,12 +659,392 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>רג'ה &amp; נתי אפ אמ - מסובב הסיבות</v>
+        <v>מייק מנג'ו - מחרוזת מלכת המועדון 2026</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>ישראל ברששת - אהבה כזאת זה אסור</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-03-20</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410081&amp;sid=05206eacbe62b6bb574609b11b437bc0</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-03-20</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>ישראל ברששת - אהבה כזאת זה אסור</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>טל ועקנין - לה לה גם בתקופות הכי קשות</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-03-20</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410080&amp;sid=05206eacbe62b6bb574609b11b437bc0</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-03-20</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>טל ועקנין - לה לה גם בתקופות הכי קשות</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>טל בן גיגי - מאה אלף</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-03-20</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410079&amp;sid=05206eacbe62b6bb574609b11b437bc0</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-03-20</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>טל בן גיגי - מאה אלף</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>חזי כהן - כשהכל נשבר</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-03-20</v>
+      </c>
+      <c r="C11" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410078&amp;sid=05206eacbe62b6bb574609b11b437bc0</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-03-20</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>חזי כהן - כשהכל נשבר</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>חגית וייסלר - בשבילך כמו אלוקים</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-03-20</v>
+      </c>
+      <c r="C12" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410077&amp;sid=05206eacbe62b6bb574609b11b437bc0</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-03-20</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>חגית וייסלר - בשבילך כמו אלוקים</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>דניאל חן - לב אחד (עם ישראל חי)</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2026-03-20</v>
+      </c>
+      <c r="C13" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410076&amp;sid=05206eacbe62b6bb574609b11b437bc0</v>
+      </c>
+      <c r="D13" t="str">
+        <v>2026-03-20</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v>דניאל חן - לב אחד (עם ישראל חי)</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>בן יוסף דניאל - האריה אם ישאג</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2026-03-20</v>
+      </c>
+      <c r="C14" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410075&amp;sid=05206eacbe62b6bb574609b11b437bc0</v>
+      </c>
+      <c r="D14" t="str">
+        <v>2026-03-20</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <v>בן יוסף דניאל - האריה אם ישאג</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>9 מילימטר - פנטזיות על אימפריה</v>
+      </c>
+      <c r="B15" t="str">
+        <v>2026-03-20</v>
+      </c>
+      <c r="C15" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410074&amp;sid=05206eacbe62b6bb574609b11b437bc0</v>
+      </c>
+      <c r="D15" t="str">
+        <v>2026-03-20</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <v/>
+      </c>
+      <c r="L15" t="str">
+        <v>9 מילימטר - פנטזיות על אימפריה</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>אייל גולן - בית מזכוכית</v>
+      </c>
+      <c r="B16" t="str">
+        <v>2026-03-20</v>
+      </c>
+      <c r="C16" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410073&amp;sid=05206eacbe62b6bb574609b11b437bc0</v>
+      </c>
+      <c r="D16" t="str">
+        <v>2026-03-20</v>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
+      <c r="K16" t="str">
+        <v/>
+      </c>
+      <c r="L16" t="str">
+        <v>אייל גולן - בית מזכוכית</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>אופיר ברמי - אתה המלך</v>
+      </c>
+      <c r="B17" t="str">
+        <v>2026-03-20</v>
+      </c>
+      <c r="C17" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410072&amp;sid=05206eacbe62b6bb574609b11b437bc0</v>
+      </c>
+      <c r="D17" t="str">
+        <v>2026-03-20</v>
+      </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
+        <v/>
+      </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
+      <c r="H17" t="str">
+        <v/>
+      </c>
+      <c r="I17" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J17" t="str">
+        <v/>
+      </c>
+      <c r="K17" t="str">
+        <v/>
+      </c>
+      <c r="L17" t="str">
+        <v>אופיר ברמי - אתה המלך</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L17"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-03-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-03-week03/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אייל גולן – בית מזכוכית</v>
+        <v>זיו כהן – ימי הביניים</v>
       </c>
       <c r="B2" t="str">
         <v>2026-03-21</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%99%d7%99%d7%9c-%d7%92%d7%95%d7%9c%d7%9f-%d7%91%d7%99%d7%aa-%d7%9e%d7%96%d7%9b%d7%95%d7%9b%d7%99%d7%aa/</v>
+        <v>https://yosmusic.com/%d7%96%d7%99%d7%95-%d7%9b%d7%94%d7%9f-%d7%99%d7%9e%d7%99-%d7%94%d7%91%d7%99%d7%a0%d7%99%d7%99%d7%9d/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-21</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>מצד אחד השיר “בית מזכוכית” של אייל גולן הוא  בלדת רגש קלאסית, עשויה היטב. מצד שני – טקסט שמבקש אמפתיה ציבורית מדמות ציבורית שנויה במחלוקת. זה שיר שמנסה להפוך ביקורת ציבורית לכאב אישי – בהצלחה מוזיקלית, אבל עם מורכבות רעיונית</v>
+        <v>השיר “ימי הביניים” של זיו כהן מנסה לעשות מהלך שאפתני: לקחת ראפ אישי ועכשווי – ולהלביש עליו עולם דימויים היסטורי־אפי. התוצאה היא שיר שמתקיים בין שני צירים: פנימי (נפשי) ו־חיצוני (מיתולוגי/היסטורי). זה שיר שמצליח לייצר אווירה חזקה וזהות סאונדית ייחודית,</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אייל גולן – בית מזכוכית</v>
+        <v>זיו כהן – ימי הביניים</v>
       </c>
     </row>
   </sheetData>
